--- a/data/trans_camb/IQ2606_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IQ2606_R2-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-10,45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14,08</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,2</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,49</t>
+          <t>14,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,28</t>
+          <t>16,35</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -0,82</t>
+          <t>-10,88; 6,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 21,76</t>
+          <t>8,94; 25,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 7,12</t>
+          <t>-19,93; -2,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 25,94</t>
+          <t>4,03; 21,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,59; -0,28</t>
+          <t>-12,43; -0,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 21,54</t>
+          <t>8,72; 21,23</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-2,79%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-12,91%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,79%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -1,15</t>
+          <t>-13,24; 9,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 28,38</t>
+          <t>11,25; 35,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 9,65</t>
+          <t>-23,51; -3,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,99; 35,86</t>
+          <t>5,66; 28,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,17; -0,34</t>
+          <t>-15,05; -0,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,41; 28,24</t>
+          <t>10,97; 27,92</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,11</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>6,25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>24,35</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13,41</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,83</t>
+          <t>23,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,52</t>
+          <t>20,23</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 12,96</t>
+          <t>7,32; 19,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,84; 29,66</t>
+          <t>8,56; 26,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 19,16</t>
+          <t>0,19; 13,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,8; 26,23</t>
+          <t>15,59; 29,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 14,66</t>
+          <t>5,63; 14,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,98; 26,18</t>
+          <t>13,87; 25,77</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,51%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26,34%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>8,57%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>33,42%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,51%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 19,12</t>
+          <t>10,21; 30,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,58; 42,75</t>
+          <t>12,51; 40,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 30,04</t>
+          <t>0,24; 19,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,06; 39,81</t>
+          <t>21,18; 43,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,0; 21,8</t>
+          <t>7,74; 21,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,12; 38,1</t>
+          <t>19,26; 37,84</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19,62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>36,62</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>19,09</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>20,21</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,62</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36,26</t>
+          <t>19,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,21</t>
+          <t>29,14</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 27,56</t>
+          <t>11,78; 27,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 32,76</t>
+          <t>25,57; 45,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 28,64</t>
+          <t>9,94; 26,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,92; 45,58</t>
+          <t>5,9; 32,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,09; 25,23</t>
+          <t>13,53; 25,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,34; 37,23</t>
+          <t>19,85; 36,69</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37,25%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>69,51%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>33,41%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>35,37%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,46; 52,62</t>
+          <t>20,48; 58,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,57; 63,15</t>
+          <t>43,88; 94,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,09; 62,04</t>
+          <t>15,69; 49,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44,25; 95,32</t>
+          <t>10,11; 61,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,65; 49,54</t>
+          <t>23,27; 50,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,77; 72,95</t>
+          <t>34,58; 71,02</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28,29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>49,64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>25,96</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>38,87</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28,29</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49,6</t>
+          <t>38,71</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,63</t>
+          <t>44,51</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,57; 34,68</t>
+          <t>20,22; 36,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,66; 49,49</t>
+          <t>37,95; 58,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,11; 35,36</t>
+          <t>18,06; 34,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,11; 59,0</t>
+          <t>27,8; 49,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,65; 33,04</t>
+          <t>21,41; 33,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,21; 51,44</t>
+          <t>35,82; 51,29</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>91,05%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>159,73%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>68,15%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>102,04%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>91,05%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159,59%</t>
+          <t>101,62%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>129,35%</t>
+          <t>129,0%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>37,19; 102,62</t>
+          <t>56,35; 137,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>61,05; 148,09</t>
+          <t>107,28; 222,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,55; 129,32</t>
+          <t>42,64; 106,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>110,79; 222,9</t>
+          <t>64,46; 145,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,18; 104,31</t>
+          <t>57,28; 108,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>99,81; 163,85</t>
+          <t>95,9; 165,03</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15,81</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>28,1</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>10,93</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>21,57</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15,81</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28,13</t>
+          <t>20,62</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,06</t>
+          <t>24,6</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,09</t>
+          <t>12,05; 19,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,17; 26,66</t>
+          <t>22,41; 32,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,89; 19,98</t>
+          <t>6,59; 14,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,44; 33,34</t>
+          <t>14,03; 26,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,49; 16,29</t>
+          <t>10,45; 16,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,1; 28,76</t>
+          <t>20,05; 28,52</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>27,47%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>48,81%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>17,6%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>34,72%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>27,47%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10,32; 25,11</t>
+          <t>20,05; 36,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24,02; 44,05</t>
+          <t>38,09; 59,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,88; 36,92</t>
+          <t>10,25; 25,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38,02; 59,66</t>
+          <t>22,51; 44,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,15; 27,92</t>
+          <t>16,96; 27,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,48; 49,36</t>
+          <t>32,91; 48,94</t>
         </is>
       </c>
     </row>
